--- a/World_Happiness_Report_Analysis.xlsx
+++ b/World_Happiness_Report_Analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Mario\Downloads\archive (2)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B6FBBA8A-C820-4D59-9A63-93D694E513D9}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B2D17E20-2DC0-4ECE-A527-398ED1273D41}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7785" activeTab="2" xr2:uid="{5A5FBD61-2001-469A-84A7-AD60DD2ECE1C}"/>
   </bookViews>
@@ -21,8 +21,9 @@
     <externalReference r:id="rId4"/>
   </externalReferences>
   <definedNames>
-    <definedName name="_xlchart.v1.0" hidden="1">'Regression_ clean'!$A$10:$A$14</definedName>
-    <definedName name="_xlchart.v1.1" hidden="1">'Regression_ clean'!$B$10:$B$14</definedName>
+    <definedName name="_xlchart.v1.0" hidden="1">'Regression_ clean'!$G$2:$G$7</definedName>
+    <definedName name="_xlchart.v1.1" hidden="1">'Regression_ clean'!$H$1</definedName>
+    <definedName name="_xlchart.v1.2" hidden="1">'Regression_ clean'!$H$2:$H$7</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -2484,688 +2485,6 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Average</a:t>
-            </a:r>
-            <a:r>
-              <a:rPr lang="en-US" baseline="0"/>
-              <a:t> Happiness Score By Year(2015-2019)</a:t>
-            </a:r>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:layout>
-        <c:manualLayout>
-          <c:xMode val="edge"/>
-          <c:yMode val="edge"/>
-          <c:x val="0.11371886997415812"/>
-          <c:y val="2.9684606895165423E-2"/>
-        </c:manualLayout>
-      </c:layout>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Regression_ clean'!$A$8</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>year</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent1"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="t"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>'Regression_ clean'!$A$9:$A$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="1">
-                  <c:v>2015</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2016</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>2019</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-B521-471E-BD1A-D5E996551DC1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>'Regression_ clean'!$B$8</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>average happiness score</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="circle"/>
-            <c:size val="5"/>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent2"/>
-              </a:solidFill>
-              <a:ln w="9525">
-                <a:solidFill>
-                  <a:schemeClr val="accent2"/>
-                </a:solidFill>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-          </c:marker>
-          <c:dLbls>
-            <c:spPr>
-              <a:noFill/>
-              <a:ln>
-                <a:noFill/>
-              </a:ln>
-              <a:effectLst/>
-            </c:spPr>
-            <c:txPr>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
-                <a:spAutoFit/>
-              </a:bodyPr>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="75000"/>
-                        <a:lumOff val="25000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:endParaRPr lang="en-US"/>
-              </a:p>
-            </c:txPr>
-            <c:dLblPos val="t"/>
-            <c:showLegendKey val="0"/>
-            <c:showVal val="1"/>
-            <c:showCatName val="0"/>
-            <c:showSerName val="0"/>
-            <c:showPercent val="0"/>
-            <c:showBubbleSize val="0"/>
-            <c:showLeaderLines val="0"/>
-            <c:extLst>
-              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="1"/>
-                <c15:leaderLines>
-                  <c:spPr>
-                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-                      <a:solidFill>
-                        <a:schemeClr val="tx1">
-                          <a:lumMod val="35000"/>
-                          <a:lumOff val="65000"/>
-                        </a:schemeClr>
-                      </a:solidFill>
-                      <a:round/>
-                    </a:ln>
-                    <a:effectLst/>
-                  </c:spPr>
-                </c15:leaderLines>
-              </c:ext>
-            </c:extLst>
-          </c:dLbls>
-          <c:val>
-            <c:numRef>
-              <c:f>'Regression_ clean'!$B$9:$B$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="1">
-                  <c:v>5.3757341772151905</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>5.3821847133757954</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>5.354019355773926</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>5.3759166666666678</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>5.4070961538461528</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-B521-471E-BD1A-D5E996551DC1}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:dLblPos val="t"/>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="1"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:marker val="1"/>
-        <c:smooth val="0"/>
-        <c:axId val="1560211935"/>
-        <c:axId val="1315144255"/>
-      </c:lineChart>
-      <c:catAx>
-        <c:axId val="1560211935"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>Average</a:t>
-                </a:r>
-                <a:r>
-                  <a:rPr lang="en-US" baseline="0"/>
-                  <a:t> happiness score</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1315144255"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblAlgn val="ctr"/>
-        <c:lblOffset val="100"/>
-        <c:noMultiLvlLbl val="0"/>
-      </c:catAx>
-      <c:valAx>
-        <c:axId val="1315144255"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:title>
-          <c:tx>
-            <c:rich>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-              <a:lstStyle/>
-              <a:p>
-                <a:pPr>
-                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                    <a:solidFill>
-                      <a:schemeClr val="tx1">
-                        <a:lumMod val="65000"/>
-                        <a:lumOff val="35000"/>
-                      </a:schemeClr>
-                    </a:solidFill>
-                    <a:latin typeface="+mn-lt"/>
-                    <a:ea typeface="+mn-ea"/>
-                    <a:cs typeface="+mn-cs"/>
-                  </a:defRPr>
-                </a:pPr>
-                <a:r>
-                  <a:rPr lang="en-US"/>
-                  <a:t>year</a:t>
-                </a:r>
-              </a:p>
-            </c:rich>
-          </c:tx>
-          <c:overlay val="0"/>
-          <c:spPr>
-            <a:noFill/>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:txPr>
-            <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-            <a:lstStyle/>
-            <a:p>
-              <a:pPr>
-                <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                  <a:solidFill>
-                    <a:schemeClr val="tx1">
-                      <a:lumMod val="65000"/>
-                      <a:lumOff val="35000"/>
-                    </a:schemeClr>
-                  </a:solidFill>
-                  <a:latin typeface="+mn-lt"/>
-                  <a:ea typeface="+mn-ea"/>
-                  <a:cs typeface="+mn-cs"/>
-                </a:defRPr>
-              </a:pPr>
-              <a:endParaRPr lang="en-US"/>
-            </a:p>
-          </c:txPr>
-        </c:title>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="1560211935"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:legend>
-      <c:legendPos val="b"/>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:legend>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:gradFill>
-        <a:gsLst>
-          <a:gs pos="0">
-            <a:schemeClr val="accent1">
-              <a:lumMod val="5000"/>
-              <a:lumOff val="95000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="74000">
-            <a:schemeClr val="accent1">
-              <a:lumMod val="45000"/>
-              <a:lumOff val="55000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="83000">
-            <a:schemeClr val="accent1">
-              <a:lumMod val="45000"/>
-              <a:lumOff val="55000"/>
-            </a:schemeClr>
-          </a:gs>
-          <a:gs pos="100000">
-            <a:schemeClr val="accent1">
-              <a:lumMod val="30000"/>
-              <a:lumOff val="70000"/>
-            </a:schemeClr>
-          </a:gs>
-        </a:gsLst>
-        <a:lin ang="5400000" scaled="1"/>
-      </a:gradFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
               <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" cap="none" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="lt1">
@@ -8205,7 +7524,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -8544,7 +7863,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -13609,7 +12928,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -13643,23 +12962,28 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="en-US">
-                <a:latin typeface="Arial Black" panose="020B0A04020102020204" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t>line</a:t>
+              <a:rPr lang="en-US"/>
+              <a:t>Average</a:t>
             </a:r>
             <a:r>
-              <a:rPr lang="en-US" baseline="0">
-                <a:latin typeface="Arial Black" panose="020B0A04020102020204" pitchFamily="34" charset="0"/>
-              </a:rPr>
-              <a:t> chart for years and average happiness</a:t>
+              <a:rPr lang="en-US" baseline="0"/>
+              <a:t> Happiness Score by Year(2015-2019)</a:t>
             </a:r>
-            <a:endParaRPr lang="en-US">
-              <a:latin typeface="Arial Black" panose="020B0A04020102020204" pitchFamily="34" charset="0"/>
-            </a:endParaRPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>  </a:t>
+            </a:r>
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.14759733158355207"/>
+          <c:y val="3.7037037037037035E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -13693,57 +13017,22 @@
     <c:plotArea>
       <c:layout/>
       <c:lineChart>
-        <c:grouping val="stacked"/>
+        <c:grouping val="standard"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:val>
-            <c:numRef>
-              <c:f>'Regression_ clean'!$A$10:$A$14</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'Regression_ clean'!$B$8</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>2015</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>2016</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>2017</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>2018</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>2019</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-725F-46CB-8BE1-232EE018E699}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
+                  <c:v>average happiness score</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
           <c:spPr>
             <a:ln w="28575" cap="rnd">
               <a:solidFill>
@@ -13756,6 +13045,30 @@
           <c:marker>
             <c:symbol val="none"/>
           </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>'Regression_ clean'!$A$10:$A$14</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2015</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2017</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2018</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>2019</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
           <c:val>
             <c:numRef>
               <c:f>'Regression_ clean'!$B$10:$B$14</c:f>
@@ -13783,7 +13096,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-725F-46CB-8BE1-232EE018E699}"/>
+              <c16:uniqueId val="{00000001-5DF9-4147-A12F-CB12C3601CA5}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -13796,16 +13109,17 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1582917519"/>
-        <c:axId val="1809082575"/>
+        <c:axId val="1592537951"/>
+        <c:axId val="1579751391"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="1582917519"/>
+        <c:axId val="1592537951"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -13842,7 +13156,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1809082575"/>
+        <c:crossAx val="1579751391"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13850,7 +13164,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1809082575"/>
+        <c:axId val="1579751391"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13901,7 +13215,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1582917519"/>
+        <c:crossAx val="1592537951"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13945,7 +13259,7 @@
       </c:txPr>
     </c:legend>
     <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="zero"/>
+    <c:dispBlanksAs val="gap"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -14149,46 +13463,6 @@
 </file>
 
 <file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
-  <a:schemeClr val="accent1"/>
-  <a:schemeClr val="accent2"/>
-  <a:schemeClr val="accent3"/>
-  <a:schemeClr val="accent4"/>
-  <a:schemeClr val="accent5"/>
-  <a:schemeClr val="accent6"/>
-  <cs:variation/>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-    <a:lumOff val="20000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="80000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="60000"/>
-    <a:lumOff val="40000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-    <a:lumOff val="30000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="70000"/>
-  </cs:variation>
-  <cs:variation>
-    <a:lumMod val="50000"/>
-    <a:lumOff val="50000"/>
-  </cs:variation>
-</cs:colorStyle>
-</file>
-
-<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -14745,527 +14019,6 @@
 </file>
 
 <file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
-<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="276">
-  <cs:axisTitle>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:axisTitle>
-  <cs:categoryAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:categoryAxis>
-  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="bg1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="1000" kern="1200"/>
-  </cs:chartArea>
-  <cs:dataLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="75000"/>
-        <a:lumOff val="25000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataLabel>
-  <cs:dataLabelCallout>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="dk1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln>
-        <a:solidFill>
-          <a:schemeClr val="dk1">
-            <a:lumMod val="25000"/>
-            <a:lumOff val="75000"/>
-          </a:schemeClr>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
-      <a:spAutoFit/>
-    </cs:bodyPr>
-  </cs:dataLabelCallout>
-  <cs:dataPoint>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint>
-  <cs:dataPoint3D>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:dataPoint3D>
-  <cs:dataPointLine>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="28575" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointLine>
-  <cs:dataPointMarker>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1">
-      <cs:styleClr val="auto"/>
-    </cs:fillRef>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointMarker>
-  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
-  <cs:dataPointWireframe>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="1"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dataPointWireframe>
-  <cs:dataTable>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:dataTable>
-  <cs:downBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="dk1">
-          <a:lumMod val="75000"/>
-          <a:lumOff val="25000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:downBar>
-  <cs:dropLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:dropLine>
-  <cs:errorBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:errorBar>
-  <cs:floor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:floor>
-  <cs:gridlineMajor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMajor>
-  <cs:gridlineMinor>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="5000"/>
-            <a:lumOff val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:gridlineMinor>
-  <cs:hiLoLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="50000"/>
-            <a:lumOff val="50000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:hiLoLine>
-  <cs:leaderLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:leaderLine>
-  <cs:legend>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:legend>
-  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea>
-  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-  </cs:plotArea3D>
-  <cs:seriesAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="15000"/>
-            <a:lumOff val="85000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:seriesAxis>
-  <cs:seriesLine>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="35000"/>
-            <a:lumOff val="65000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:seriesLine>
-  <cs:title>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
-  </cs:title>
-  <cs:trendline>
-    <cs:lnRef idx="0">
-      <cs:styleClr val="auto"/>
-    </cs:lnRef>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:ln w="19050" cap="rnd">
-        <a:solidFill>
-          <a:schemeClr val="phClr"/>
-        </a:solidFill>
-        <a:prstDash val="sysDot"/>
-      </a:ln>
-    </cs:spPr>
-  </cs:trendline>
-  <cs:trendlineLabel>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:trendlineLabel>
-  <cs:upBar>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:solidFill>
-        <a:schemeClr val="lt1"/>
-      </a:solidFill>
-      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-        <a:solidFill>
-          <a:schemeClr val="tx1">
-            <a:lumMod val="65000"/>
-            <a:lumOff val="35000"/>
-          </a:schemeClr>
-        </a:solidFill>
-        <a:round/>
-      </a:ln>
-    </cs:spPr>
-  </cs:upBar>
-  <cs:valueAxis>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1">
-        <a:lumMod val="65000"/>
-        <a:lumOff val="35000"/>
-      </a:schemeClr>
-    </cs:fontRef>
-    <cs:defRPr sz="900" kern="1200"/>
-  </cs:valueAxis>
-  <cs:wall>
-    <cs:lnRef idx="0"/>
-    <cs:fillRef idx="0"/>
-    <cs:effectRef idx="0"/>
-    <cs:fontRef idx="minor">
-      <a:schemeClr val="tx1"/>
-    </cs:fontRef>
-    <cs:spPr>
-      <a:noFill/>
-      <a:ln>
-        <a:noFill/>
-      </a:ln>
-    </cs:spPr>
-  </cs:wall>
-</cs:chartStyle>
-</file>
-
-<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="245">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -15803,7 +14556,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -16306,7 +15059,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="245">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -16844,7 +15597,7 @@
 </cs:chartStyle>
 </file>
 
-<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/style5.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -17405,42 +16158,6 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>57150</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>28573</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>257175</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:to>
-    <xdr:graphicFrame macro="">
-      <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="6" name="Chart 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16A2110A-3C27-4EBF-BCEA-5DD22FE5CAD2}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvGraphicFramePr/>
-      </xdr:nvGraphicFramePr>
-      <xdr:xfrm>
-        <a:off x="0" y="0"/>
-        <a:ext cx="0" cy="0"/>
-      </xdr:xfrm>
-      <a:graphic>
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </xdr:graphicFrame>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>47624</xdr:colOff>
       <xdr:row>0</xdr:row>
@@ -17449,8 +16166,8 @@
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>104774</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -17469,7 +16186,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -17505,7 +16222,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -17513,16 +16230,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>2152650</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>157162</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>1</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>42862</xdr:rowOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>1600200</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>57151</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -17541,7 +16258,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -17549,23 +16266,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>15</xdr:row>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>47626</xdr:colOff>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>9525</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>28575</xdr:colOff>
-      <xdr:row>26</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>147636</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
-        <xdr:cNvPr id="9" name="Chart 8">
+        <xdr:cNvPr id="13" name="Chart 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{29DDCA12-4D3B-4A93-8FA9-23A744B7C234}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A0BF53F-3758-45B1-999E-916B1D2263F5}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -17577,7 +16294,7 @@
       </xdr:xfrm>
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
